--- a/Supplementary_Materials/detection_tptnfpfn.xlsx
+++ b/Supplementary_Materials/detection_tptnfpfn.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Desktop\Supplementary_Materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A11D4E76-5CA4-410A-82BE-D16273EB32E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F399CAA9-635A-4200-9BF3-0F71829D712B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="39">
   <si>
     <t>Model</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -163,6 +163,26 @@
   </si>
   <si>
     <t>5.4:  RCA-verified Result</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gpt-oss:120b ≈o4-mini</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P-C</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P-V</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P-B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>P-R</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -234,7 +254,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -266,11 +286,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDEE0E3"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDEE0E3"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -294,11 +327,34 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="14">
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -611,10 +667,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{88CA140E-7B21-49D9-8C53-10532143A179}" name="表2" displayName="表2" ref="A2:I5" totalsRowShown="0">
-  <autoFilter ref="A2:I5" xr:uid="{88CA140E-7B21-49D9-8C53-10532143A179}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{88CA140E-7B21-49D9-8C53-10532143A179}" name="表2" displayName="表2" ref="A2:I6" totalsRowShown="0">
+  <autoFilter ref="A2:I6" xr:uid="{88CA140E-7B21-49D9-8C53-10532143A179}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{3599CD0A-29F7-40B5-B678-FB9EDF2364EC}" name="Model" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{3599CD0A-29F7-40B5-B678-FB9EDF2364EC}" name="Model" dataDxfId="13"/>
     <tableColumn id="2" xr3:uid="{5AC6376B-5EB3-47BC-8586-471E1888F0C7}" name="TP"/>
     <tableColumn id="3" xr3:uid="{12E9AFF4-C7A8-442C-BF37-D729453435FE}" name="TN"/>
     <tableColumn id="4" xr3:uid="{DE35441A-AF6F-4F39-8388-C0898A4C0F33}" name="FP"/>
@@ -629,10 +685,10 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{155D92FD-02B0-407A-9C5C-CFD33AEA1E73}" name="表3" displayName="表3" ref="K2:S5" totalsRowShown="0">
-  <autoFilter ref="K2:S5" xr:uid="{155D92FD-02B0-407A-9C5C-CFD33AEA1E73}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{0EB1CB38-3798-4740-AD37-70798E871088}" name="Model" dataDxfId="8"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{155D92FD-02B0-407A-9C5C-CFD33AEA1E73}" name="表3" displayName="表3" ref="K2:W6" totalsRowShown="0">
+  <autoFilter ref="K2:W6" xr:uid="{155D92FD-02B0-407A-9C5C-CFD33AEA1E73}"/>
+  <tableColumns count="13">
+    <tableColumn id="1" xr3:uid="{0EB1CB38-3798-4740-AD37-70798E871088}" name="Model" dataDxfId="12"/>
     <tableColumn id="2" xr3:uid="{7CDE3FC9-CCBA-4685-904D-3E0F06E89C38}" name="TP"/>
     <tableColumn id="3" xr3:uid="{FD330268-3D03-44B1-B6D2-CB2974EDD466}" name="TN"/>
     <tableColumn id="4" xr3:uid="{8491126D-16AA-42E9-AACE-BAB8B212BA34}" name="FP"/>
@@ -641,16 +697,20 @@
     <tableColumn id="7" xr3:uid="{2A9F603B-4B2B-441E-8F96-C0E64D8B280C}" name="Recall"/>
     <tableColumn id="8" xr3:uid="{D8BB11E1-7308-4242-BAD5-7E7F1F044262}" name="F1"/>
     <tableColumn id="9" xr3:uid="{FB0A8A80-B453-45D8-B4CD-DC9D7C6D7780}" name="Accuracy"/>
+    <tableColumn id="10" xr3:uid="{38F6E6FC-19A4-4540-A065-9BFE82F155D5}" name="P-C" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{3431DAF4-954A-439A-B129-16A7B9149092}" name="P-V" dataDxfId="2"/>
+    <tableColumn id="13" xr3:uid="{A5012397-4054-4842-B30D-1782BE044013}" name="P-B" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{0F284BB8-79F8-4595-8326-90B7D4DDFD31}" name="P-R" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{81F1B3FD-B3DD-428D-B811-6E96F15E653C}" name="表2_5" displayName="表2_5" ref="A9:I14" totalsRowShown="0">
-  <autoFilter ref="A9:I14" xr:uid="{81F1B3FD-B3DD-428D-B811-6E96F15E653C}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{81F1B3FD-B3DD-428D-B811-6E96F15E653C}" name="表2_5" displayName="表2_5" ref="A10:I15" totalsRowShown="0">
+  <autoFilter ref="A10:I15" xr:uid="{81F1B3FD-B3DD-428D-B811-6E96F15E653C}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C408C6B2-77A7-4CCF-B296-67DAACCBE024}" name="Method" dataDxfId="7"/>
+    <tableColumn id="1" xr3:uid="{C408C6B2-77A7-4CCF-B296-67DAACCBE024}" name="Method" dataDxfId="11"/>
     <tableColumn id="2" xr3:uid="{6AAC990C-7814-4010-BB7C-BE84EFC80B96}" name="TP"/>
     <tableColumn id="3" xr3:uid="{D244E047-F1AA-441B-A547-BED64B38EEC2}" name="TN"/>
     <tableColumn id="4" xr3:uid="{52F33817-11DB-4561-BACE-EB0B2E9D71AA}" name="FP"/>
@@ -665,10 +725,10 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ED1EDC30-AEF7-4AEC-A90A-83EADE6E72F5}" name="表2_57" displayName="表2_57" ref="K9:S14" totalsRowShown="0">
-  <autoFilter ref="K9:S14" xr:uid="{ED1EDC30-AEF7-4AEC-A90A-83EADE6E72F5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ED1EDC30-AEF7-4AEC-A90A-83EADE6E72F5}" name="表2_57" displayName="表2_57" ref="K10:S15" totalsRowShown="0">
+  <autoFilter ref="K10:S15" xr:uid="{ED1EDC30-AEF7-4AEC-A90A-83EADE6E72F5}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{9FA1EFE9-0573-42A3-87DC-58163D885660}" name="Method" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{9FA1EFE9-0573-42A3-87DC-58163D885660}" name="Method" dataDxfId="10"/>
     <tableColumn id="2" xr3:uid="{21010D3A-A70D-46B3-BE1B-4EEC4575F824}" name="TP"/>
     <tableColumn id="3" xr3:uid="{6B91F050-B52B-4957-BE4B-2F25B524D6FD}" name="TN"/>
     <tableColumn id="4" xr3:uid="{44C9D43F-9A4A-4271-8E38-658108C43E5A}" name="FP"/>
@@ -683,11 +743,11 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4A47D4AF-C1F4-4B2E-84E2-C1BE29BA7CC4}" name="表2_59" displayName="表2_59" ref="A18:I23" totalsRowShown="0">
-  <autoFilter ref="A18:I23" xr:uid="{4A47D4AF-C1F4-4B2E-84E2-C1BE29BA7CC4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4A47D4AF-C1F4-4B2E-84E2-C1BE29BA7CC4}" name="表2_59" displayName="表2_59" ref="A19:I24" totalsRowShown="0">
+  <autoFilter ref="A19:I24" xr:uid="{4A47D4AF-C1F4-4B2E-84E2-C1BE29BA7CC4}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{BCF58236-26AE-40C9-9599-9A59EC7450B2}" name="ID" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{CF45B29B-BE5A-4FDA-8803-A8923237A0F0}" name="TP" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{BCF58236-26AE-40C9-9599-9A59EC7450B2}" name="ID" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{CF45B29B-BE5A-4FDA-8803-A8923237A0F0}" name="TP" dataDxfId="8"/>
     <tableColumn id="3" xr3:uid="{F54E13CD-EBFC-4829-A77E-8E1C7890803D}" name="TN"/>
     <tableColumn id="4" xr3:uid="{F759BB32-5E40-40A9-A0B9-89FF3B4FF21C}" name="FP"/>
     <tableColumn id="5" xr3:uid="{73042ED4-CE53-4E99-B6AF-9BD2999205C5}" name="FN"/>
@@ -701,10 +761,10 @@
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D9F59797-4543-40C3-956A-134AD5BD8027}" name="表9" displayName="表9" ref="A27:I30" totalsRowShown="0">
-  <autoFilter ref="A27:I30" xr:uid="{D9F59797-4543-40C3-956A-134AD5BD8027}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D9F59797-4543-40C3-956A-134AD5BD8027}" name="表9" displayName="表9" ref="A28:I31" totalsRowShown="0">
+  <autoFilter ref="A28:I31" xr:uid="{D9F59797-4543-40C3-956A-134AD5BD8027}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{2E1F777C-801F-427C-9438-9D669CB2CC5F}" name="Dataset" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{2E1F777C-801F-427C-9438-9D669CB2CC5F}" name="Dataset" dataDxfId="7"/>
     <tableColumn id="2" xr3:uid="{2996D0E9-0986-4099-A9E6-4829F00A64A6}" name="TP"/>
     <tableColumn id="3" xr3:uid="{A9DA785A-2CFA-4A90-924D-3B371F83F26B}" name="TN"/>
     <tableColumn id="4" xr3:uid="{6C096669-A4B5-4BE8-B8F4-FFB7ABF2C8C6}" name="FP"/>
@@ -719,11 +779,11 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E45B7DE5-6884-4AAB-B0E8-948C8ECAE034}" name="表2_5911" displayName="表2_5911" ref="K18:S23" totalsRowShown="0">
-  <autoFilter ref="K18:S23" xr:uid="{E45B7DE5-6884-4AAB-B0E8-948C8ECAE034}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E45B7DE5-6884-4AAB-B0E8-948C8ECAE034}" name="表2_5911" displayName="表2_5911" ref="K19:S24" totalsRowShown="0">
+  <autoFilter ref="K19:S24" xr:uid="{E45B7DE5-6884-4AAB-B0E8-948C8ECAE034}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{8CF70A89-BE48-4C01-9D7E-FDD1454C61A5}" name="ID" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{25C65B6D-EA69-4471-81D4-43E1464B9339}" name="TP" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{8CF70A89-BE48-4C01-9D7E-FDD1454C61A5}" name="ID" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{25C65B6D-EA69-4471-81D4-43E1464B9339}" name="TP" dataDxfId="5"/>
     <tableColumn id="3" xr3:uid="{1AC6B611-57E5-41B0-B363-BB9D2A11A53A}" name="TN"/>
     <tableColumn id="4" xr3:uid="{53A506B5-237A-4F73-9FFB-FC1053E0DCBD}" name="FP"/>
     <tableColumn id="5" xr3:uid="{C0693F33-0CFC-4212-AB5F-B454ADBE77DD}" name="FN"/>
@@ -737,10 +797,10 @@
 </file>
 
 <file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{AFCC0346-4AFC-429E-87BD-CA9C9458A5B9}" name="表9_12" displayName="表9_12" ref="K27:S30" totalsRowShown="0">
-  <autoFilter ref="K27:S30" xr:uid="{AFCC0346-4AFC-429E-87BD-CA9C9458A5B9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{AFCC0346-4AFC-429E-87BD-CA9C9458A5B9}" name="表9_12" displayName="表9_12" ref="K28:S31" totalsRowShown="0">
+  <autoFilter ref="K28:S31" xr:uid="{AFCC0346-4AFC-429E-87BD-CA9C9458A5B9}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F9DAA578-1F1C-4469-BD21-048F1801D7B7}" name="Dataset" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{F9DAA578-1F1C-4469-BD21-048F1801D7B7}" name="Dataset" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{6FB60BB2-0755-491E-933F-23FEDF9286B8}" name="TP"/>
     <tableColumn id="3" xr3:uid="{B25EE914-F2EE-443B-85F9-3D87F49A2A92}" name="TN"/>
     <tableColumn id="4" xr3:uid="{4C8FF114-96A0-4D3A-955A-FEBF9B2E5619}" name="FP"/>
@@ -1017,7 +1077,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:W31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="6" max="6" width="10.5" customWidth="1"/>
@@ -1026,7 +1086,7 @@
     <col min="19" max="19" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A1" s="12" t="s">
         <v>20</v>
       </c>
@@ -1050,7 +1110,7 @@
       <c r="R1" s="12"/>
       <c r="S1" s="12"/>
     </row>
-    <row r="2" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -1105,64 +1165,88 @@
       <c r="S2" t="s">
         <v>11</v>
       </c>
+      <c r="T2" t="s">
+        <v>35</v>
+      </c>
+      <c r="U2" t="s">
+        <v>36</v>
+      </c>
+      <c r="V2" t="s">
+        <v>37</v>
+      </c>
+      <c r="W2" t="s">
+        <v>38</v>
+      </c>
     </row>
-    <row r="3" spans="1:20" ht="39" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>354</v>
-      </c>
-      <c r="C3">
-        <v>244</v>
-      </c>
-      <c r="D3">
-        <v>253</v>
-      </c>
-      <c r="E3">
-        <v>143</v>
-      </c>
-      <c r="F3" s="2">
-        <v>0.58320000000000005</v>
-      </c>
-      <c r="G3" s="2">
-        <v>0.71230000000000004</v>
-      </c>
-      <c r="H3" s="2">
-        <v>0.6431</v>
-      </c>
-      <c r="I3" s="2">
-        <v>0.60160000000000002</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="L3" s="5">
-        <v>226</v>
-      </c>
-      <c r="M3" s="7">
-        <v>443</v>
-      </c>
-      <c r="N3" s="7">
-        <v>54</v>
-      </c>
-      <c r="O3" s="5">
-        <v>271</v>
-      </c>
-      <c r="P3" s="6">
-        <v>0.80810000000000004</v>
-      </c>
-      <c r="Q3" s="6">
-        <v>0.45739999999999997</v>
-      </c>
-      <c r="R3" s="6">
-        <v>0.58169999999999999</v>
-      </c>
-      <c r="S3" s="6">
-        <v>0.67300000000000004</v>
+    <row r="3" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="5">
+        <v>366</v>
+      </c>
+      <c r="C3" s="5">
+        <v>254</v>
+      </c>
+      <c r="D3" s="5">
+        <v>243</v>
+      </c>
+      <c r="E3" s="5">
+        <v>131</v>
+      </c>
+      <c r="F3" s="6">
+        <v>0.59360000000000002</v>
+      </c>
+      <c r="G3" s="6">
+        <v>0.73050000000000004</v>
+      </c>
+      <c r="H3" s="6">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="I3" s="6">
+        <v>0.61950000000000005</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="L3">
+        <v>158</v>
+      </c>
+      <c r="M3" s="5">
+        <v>458</v>
+      </c>
+      <c r="N3" s="5">
+        <v>39</v>
+      </c>
+      <c r="O3">
+        <v>339</v>
+      </c>
+      <c r="P3" s="2">
+        <v>0.80200000000000005</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>0.31790000000000002</v>
+      </c>
+      <c r="R3" s="2">
+        <v>0.45529999999999998</v>
+      </c>
+      <c r="S3" s="2">
+        <v>0.61970000000000003</v>
+      </c>
+      <c r="T3" s="2">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="U3" s="6">
+        <v>0.05</v>
+      </c>
+      <c r="V3" s="2">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="W3" s="2">
+        <v>2.8000000000000001E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -1217,1043 +1301,1135 @@
       <c r="S4" s="2">
         <v>0.58650000000000002</v>
       </c>
+      <c r="T4" s="2">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="U4" s="2">
+        <v>8.8999999999999996E-2</v>
+      </c>
+      <c r="V4" s="2">
+        <v>0.67</v>
+      </c>
+      <c r="W4" s="2">
+        <v>3.4000000000000002E-2</v>
+      </c>
     </row>
-    <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="5">
-        <v>366</v>
-      </c>
-      <c r="C5" s="5">
-        <v>254</v>
-      </c>
-      <c r="D5" s="5">
-        <v>243</v>
-      </c>
-      <c r="E5" s="5">
-        <v>131</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0.59360000000000002</v>
-      </c>
-      <c r="G5" s="6">
-        <v>0.73050000000000004</v>
-      </c>
-      <c r="H5" s="6">
-        <v>0.65500000000000003</v>
-      </c>
-      <c r="I5" s="6">
-        <v>0.61950000000000005</v>
+    <row r="5" spans="1:23" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5">
+        <v>354</v>
+      </c>
+      <c r="C5">
+        <v>244</v>
+      </c>
+      <c r="D5">
+        <v>253</v>
+      </c>
+      <c r="E5">
+        <v>143</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.58320000000000005</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0.71230000000000004</v>
+      </c>
+      <c r="H5" s="2">
+        <v>0.6431</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0.60160000000000002</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L5">
-        <v>158</v>
-      </c>
-      <c r="M5" s="5">
-        <v>458</v>
-      </c>
-      <c r="N5" s="5">
-        <v>39</v>
-      </c>
-      <c r="O5">
-        <v>339</v>
-      </c>
-      <c r="P5" s="2">
-        <v>0.80200000000000005</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>0.31790000000000002</v>
-      </c>
-      <c r="R5" s="2">
-        <v>0.45529999999999998</v>
-      </c>
-      <c r="S5" s="2">
-        <v>0.61970000000000003</v>
+        <v>5</v>
+      </c>
+      <c r="L5" s="7">
+        <v>226</v>
+      </c>
+      <c r="M5" s="7">
+        <v>443</v>
+      </c>
+      <c r="N5" s="7">
+        <v>54</v>
+      </c>
+      <c r="O5" s="7">
+        <v>271</v>
+      </c>
+      <c r="P5" s="8">
+        <v>0.80810000000000004</v>
+      </c>
+      <c r="Q5" s="8">
+        <v>0.45739999999999997</v>
+      </c>
+      <c r="R5" s="8">
+        <v>0.58169999999999999</v>
+      </c>
+      <c r="S5" s="8">
+        <v>0.67300000000000004</v>
+      </c>
+      <c r="T5" s="8">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="U5" s="8">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="V5" s="8">
+        <v>0.52900000000000003</v>
+      </c>
+      <c r="W5" s="8">
+        <v>1.6E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A8" s="12" t="s">
+    <row r="6" spans="1:23" ht="38.25" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="14">
+        <v>368</v>
+      </c>
+      <c r="C6" s="14">
+        <v>233</v>
+      </c>
+      <c r="D6" s="14">
+        <v>264</v>
+      </c>
+      <c r="E6" s="14">
+        <v>129</v>
+      </c>
+      <c r="F6" s="15">
+        <v>0.58220000000000005</v>
+      </c>
+      <c r="G6" s="15">
+        <v>0.74039999999999995</v>
+      </c>
+      <c r="H6" s="15">
+        <v>0.65190000000000003</v>
+      </c>
+      <c r="I6" s="15">
+        <v>0.60460000000000003</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="L6" s="17">
+        <v>244</v>
+      </c>
+      <c r="M6" s="14">
+        <v>445</v>
+      </c>
+      <c r="N6" s="19">
+        <v>52</v>
+      </c>
+      <c r="O6" s="17">
+        <v>253</v>
+      </c>
+      <c r="P6" s="18">
+        <v>0.82430000000000003</v>
+      </c>
+      <c r="Q6" s="18">
+        <v>0.4909</v>
+      </c>
+      <c r="R6" s="18">
+        <v>0.61539999999999995</v>
+      </c>
+      <c r="S6" s="18">
+        <v>0.69320000000000004</v>
+      </c>
+      <c r="T6" s="18">
+        <v>0.39400000000000002</v>
+      </c>
+      <c r="U6" s="15">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="V6" s="18">
+        <v>0.501</v>
+      </c>
+      <c r="W6" s="18">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="A9" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12"/>
-      <c r="H8" s="12"/>
-      <c r="I8" s="3"/>
-      <c r="K8" s="12" t="s">
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="12"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="3"/>
+      <c r="K9" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="L8" s="12"/>
-      <c r="M8" s="12"/>
-      <c r="N8" s="12"/>
-      <c r="O8" s="12"/>
-      <c r="P8" s="12"/>
-      <c r="Q8" s="12"/>
-      <c r="R8" s="12"/>
-      <c r="S8" s="12"/>
+      <c r="L9" s="12"/>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12"/>
+      <c r="S9" s="12"/>
     </row>
-    <row r="9" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="10" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>13</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>1</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>2</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D10" t="s">
         <v>3</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E10" t="s">
         <v>4</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F10" t="s">
         <v>8</v>
       </c>
-      <c r="G9" t="s">
+      <c r="G10" t="s">
         <v>9</v>
       </c>
-      <c r="H9" t="s">
+      <c r="H10" t="s">
         <v>10</v>
       </c>
-      <c r="I9" t="s">
+      <c r="I10" t="s">
         <v>11</v>
       </c>
-      <c r="K9" t="s">
+      <c r="K10" t="s">
         <v>13</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L10" t="s">
         <v>1</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M10" t="s">
         <v>2</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N10" t="s">
         <v>3</v>
       </c>
-      <c r="O9" t="s">
+      <c r="O10" t="s">
         <v>4</v>
       </c>
-      <c r="P9" t="s">
+      <c r="P10" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="Q10" t="s">
         <v>9</v>
       </c>
-      <c r="R9" t="s">
+      <c r="R10" t="s">
         <v>10</v>
       </c>
-      <c r="S9" t="s">
+      <c r="S10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="11" spans="1:23" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>144</v>
       </c>
-      <c r="C10">
+      <c r="C11">
         <v>359</v>
       </c>
-      <c r="D10">
+      <c r="D11">
         <v>138</v>
       </c>
-      <c r="E10">
+      <c r="E11">
         <v>353</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F11" s="2">
         <v>0.51060000000000005</v>
       </c>
-      <c r="G10" s="2">
+      <c r="G11" s="2">
         <v>0.28970000000000001</v>
       </c>
-      <c r="H10" s="2">
+      <c r="H11" s="2">
         <v>0.36969999999999997</v>
       </c>
-      <c r="I10" s="2">
+      <c r="I11" s="2">
         <v>0.50600000000000001</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="K11" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="L10">
+      <c r="L11">
         <v>84</v>
       </c>
-      <c r="M10">
+      <c r="M11">
         <v>401</v>
       </c>
-      <c r="N10">
+      <c r="N11">
         <v>96</v>
       </c>
-      <c r="O10">
+      <c r="O11">
         <v>413</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P11" s="2">
         <v>0.4667</v>
       </c>
-      <c r="Q10" s="2">
+      <c r="Q11" s="2">
         <v>0.16900000000000001</v>
       </c>
-      <c r="R10" s="2">
+      <c r="R11" s="2">
         <v>0.24809999999999999</v>
       </c>
-      <c r="S10" s="2">
+      <c r="S11" s="2">
         <v>0.4879</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="12" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B11">
+      <c r="B12">
         <v>130</v>
       </c>
-      <c r="C11">
+      <c r="C12">
         <v>407</v>
       </c>
-      <c r="D11">
+      <c r="D12">
         <v>90</v>
       </c>
-      <c r="E11">
+      <c r="E12">
         <v>367</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F12" s="2">
         <v>0.59089999999999998</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G12" s="2">
         <v>0.2616</v>
       </c>
-      <c r="H11" s="2">
+      <c r="H12" s="2">
         <v>0.36259999999999998</v>
       </c>
-      <c r="I11" s="2">
+      <c r="I12" s="2">
         <v>0.54020000000000001</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="K12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L11">
+      <c r="L12">
         <v>137</v>
       </c>
-      <c r="M11">
+      <c r="M12">
         <v>438</v>
       </c>
-      <c r="N11">
+      <c r="N12">
         <v>59</v>
       </c>
-      <c r="O11">
+      <c r="O12">
         <v>360</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P12" s="2">
         <v>0.69899999999999995</v>
       </c>
-      <c r="Q11" s="2">
+      <c r="Q12" s="2">
         <v>0.2757</v>
       </c>
-      <c r="R11" s="2">
+      <c r="R12" s="2">
         <v>0.39539999999999997</v>
       </c>
-      <c r="S11" s="2">
+      <c r="S12" s="2">
         <v>0.57850000000000001</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" s="7">
-        <v>117</v>
-      </c>
-      <c r="C12" s="5">
-        <v>421</v>
-      </c>
-      <c r="D12" s="5">
-        <v>76</v>
-      </c>
-      <c r="E12" s="7">
-        <v>380</v>
-      </c>
-      <c r="F12" s="8">
-        <v>0.60599999999999998</v>
-      </c>
-      <c r="G12" s="8">
-        <v>0.2354</v>
-      </c>
-      <c r="H12" s="8">
-        <v>0.33910000000000001</v>
-      </c>
-      <c r="I12" s="8">
-        <v>0.54120000000000001</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L12" s="7">
-        <v>129</v>
-      </c>
-      <c r="M12" s="7">
-        <v>407</v>
-      </c>
-      <c r="N12" s="7">
-        <v>90</v>
-      </c>
-      <c r="O12" s="7">
-        <v>368</v>
-      </c>
-      <c r="P12" s="8">
-        <v>0.58899999999999997</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>0.2596</v>
-      </c>
-      <c r="R12" s="8">
-        <v>0.36030000000000001</v>
-      </c>
-      <c r="S12" s="8">
-        <v>0.53920000000000001</v>
       </c>
       <c r="T12" s="7"/>
     </row>
-    <row r="13" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B13" s="7">
-        <v>114</v>
-      </c>
-      <c r="C13" s="7">
-        <v>409</v>
-      </c>
-      <c r="D13" s="7">
-        <v>88</v>
+        <v>117</v>
+      </c>
+      <c r="C13" s="5">
+        <v>421</v>
+      </c>
+      <c r="D13" s="5">
+        <v>76</v>
       </c>
       <c r="E13" s="7">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="F13" s="8">
-        <v>0.56399999999999995</v>
+        <v>0.60599999999999998</v>
       </c>
       <c r="G13" s="8">
-        <v>0.22939999999999999</v>
+        <v>0.2354</v>
       </c>
       <c r="H13" s="8">
-        <v>0.32619999999999999</v>
+        <v>0.33910000000000001</v>
       </c>
       <c r="I13" s="8">
-        <v>0.5262</v>
+        <v>0.54120000000000001</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L13" s="7">
-        <v>71</v>
-      </c>
-      <c r="M13" s="5">
-        <v>473</v>
-      </c>
-      <c r="N13" s="5">
-        <v>24</v>
+        <v>129</v>
+      </c>
+      <c r="M13" s="7">
+        <v>407</v>
+      </c>
+      <c r="N13" s="7">
+        <v>90</v>
       </c>
       <c r="O13" s="7">
-        <v>426</v>
+        <v>368</v>
       </c>
       <c r="P13" s="8">
-        <v>0.74729999999999996</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="Q13" s="8">
-        <v>0.1429</v>
+        <v>0.2596</v>
       </c>
       <c r="R13" s="8">
-        <v>0.2399</v>
+        <v>0.36030000000000001</v>
       </c>
       <c r="S13" s="8">
-        <v>0.54730000000000001</v>
+        <v>0.53920000000000001</v>
       </c>
       <c r="T13" s="7"/>
     </row>
-    <row r="14" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="7">
+        <v>114</v>
+      </c>
+      <c r="C14" s="7">
+        <v>409</v>
+      </c>
+      <c r="D14" s="7">
+        <v>88</v>
+      </c>
+      <c r="E14" s="7">
+        <v>383</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0.56399999999999995</v>
+      </c>
+      <c r="G14" s="8">
+        <v>0.22939999999999999</v>
+      </c>
+      <c r="H14" s="8">
+        <v>0.32619999999999999</v>
+      </c>
+      <c r="I14" s="8">
+        <v>0.5262</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L14" s="7">
+        <v>71</v>
+      </c>
+      <c r="M14" s="5">
+        <v>473</v>
+      </c>
+      <c r="N14" s="5">
+        <v>24</v>
+      </c>
+      <c r="O14" s="7">
+        <v>426</v>
+      </c>
+      <c r="P14" s="8">
+        <v>0.74729999999999996</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>0.1429</v>
+      </c>
+      <c r="R14" s="8">
+        <v>0.2399</v>
+      </c>
+      <c r="S14" s="8">
+        <v>0.54730000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B14" s="5">
+      <c r="B15" s="5">
         <v>354</v>
       </c>
-      <c r="C14">
+      <c r="C15">
         <v>244</v>
       </c>
-      <c r="D14">
+      <c r="D15">
         <v>253</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E15" s="5">
         <v>143</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F15" s="6">
         <v>0.58320000000000005</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G15" s="6">
         <v>0.71230000000000004</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H15" s="6">
         <v>0.6431</v>
       </c>
-      <c r="I14" s="6">
+      <c r="I15" s="6">
         <v>0.60160000000000002</v>
       </c>
-      <c r="K14" s="4" t="s">
+      <c r="K15" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L15" s="5">
         <v>226</v>
       </c>
-      <c r="M14" s="7">
+      <c r="M15" s="7">
         <v>443</v>
       </c>
-      <c r="N14" s="7">
+      <c r="N15" s="7">
         <v>54</v>
       </c>
-      <c r="O14" s="5">
+      <c r="O15" s="5">
         <v>271</v>
       </c>
-      <c r="P14" s="6">
+      <c r="P15" s="6">
         <v>0.80810000000000004</v>
       </c>
-      <c r="Q14" s="6">
+      <c r="Q15" s="6">
         <v>0.45739999999999997</v>
       </c>
-      <c r="R14" s="6">
+      <c r="R15" s="6">
         <v>0.58169999999999999</v>
       </c>
-      <c r="S14" s="6">
+      <c r="S15" s="6">
         <v>0.67300000000000004</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A17" s="12" t="s">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A18" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="3"/>
-      <c r="K17" s="12" t="s">
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="K18" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-    </row>
-    <row r="18" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1</v>
-      </c>
-      <c r="C18" t="s">
-        <v>2</v>
-      </c>
-      <c r="D18" t="s">
-        <v>3</v>
-      </c>
-      <c r="E18" t="s">
-        <v>4</v>
-      </c>
-      <c r="F18" t="s">
-        <v>8</v>
-      </c>
-      <c r="G18" t="s">
-        <v>9</v>
-      </c>
-      <c r="H18" t="s">
-        <v>10</v>
-      </c>
-      <c r="I18" t="s">
-        <v>11</v>
-      </c>
-      <c r="K18" t="s">
-        <v>23</v>
-      </c>
-      <c r="L18" t="s">
-        <v>1</v>
-      </c>
-      <c r="M18" t="s">
-        <v>2</v>
-      </c>
-      <c r="N18" t="s">
-        <v>3</v>
-      </c>
-      <c r="O18" t="s">
-        <v>4</v>
-      </c>
-      <c r="P18" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>9</v>
-      </c>
-      <c r="R18" t="s">
-        <v>10</v>
-      </c>
-      <c r="S18" t="s">
-        <v>11</v>
-      </c>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
     </row>
     <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="9">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
         <v>1</v>
       </c>
-      <c r="B19">
-        <v>126</v>
-      </c>
-      <c r="C19">
-        <v>399</v>
-      </c>
-      <c r="D19">
-        <v>98</v>
-      </c>
-      <c r="E19">
-        <v>371</v>
-      </c>
-      <c r="F19" s="2">
-        <v>0.5625</v>
-      </c>
-      <c r="G19" s="2">
-        <v>0.2535</v>
-      </c>
-      <c r="H19" s="2">
-        <v>0.34949999999999998</v>
-      </c>
-      <c r="I19" s="2">
-        <v>0.5282</v>
-      </c>
-      <c r="K19" s="9">
+      <c r="C19" t="s">
+        <v>2</v>
+      </c>
+      <c r="D19" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" t="s">
+        <v>4</v>
+      </c>
+      <c r="F19" t="s">
+        <v>8</v>
+      </c>
+      <c r="G19" t="s">
+        <v>9</v>
+      </c>
+      <c r="H19" t="s">
+        <v>10</v>
+      </c>
+      <c r="I19" t="s">
+        <v>11</v>
+      </c>
+      <c r="K19" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" t="s">
         <v>1</v>
       </c>
-      <c r="L19">
-        <v>84</v>
-      </c>
-      <c r="M19">
-        <v>461</v>
-      </c>
-      <c r="N19">
-        <v>36</v>
-      </c>
-      <c r="O19">
-        <v>413</v>
-      </c>
-      <c r="P19" s="2">
-        <v>0.7</v>
-      </c>
-      <c r="Q19" s="2">
-        <v>0.16900000000000001</v>
-      </c>
-      <c r="R19" s="2">
-        <v>0.27229999999999999</v>
-      </c>
-      <c r="S19" s="2">
-        <v>0.54830000000000001</v>
+      <c r="M19" t="s">
+        <v>2</v>
+      </c>
+      <c r="N19" t="s">
+        <v>3</v>
+      </c>
+      <c r="O19" t="s">
+        <v>4</v>
+      </c>
+      <c r="P19" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>9</v>
+      </c>
+      <c r="R19" t="s">
+        <v>10</v>
+      </c>
+      <c r="S19" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+      <c r="A20" s="9">
+        <v>1</v>
+      </c>
+      <c r="B20">
+        <v>126</v>
+      </c>
+      <c r="C20">
+        <v>399</v>
+      </c>
+      <c r="D20">
+        <v>98</v>
+      </c>
+      <c r="E20">
+        <v>371</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.5625</v>
+      </c>
+      <c r="G20" s="2">
+        <v>0.2535</v>
+      </c>
+      <c r="H20" s="2">
+        <v>0.34949999999999998</v>
+      </c>
+      <c r="I20" s="2">
+        <v>0.5282</v>
+      </c>
+      <c r="K20" s="9">
+        <v>1</v>
+      </c>
+      <c r="L20">
+        <v>84</v>
+      </c>
+      <c r="M20">
+        <v>461</v>
+      </c>
+      <c r="N20">
+        <v>36</v>
+      </c>
+      <c r="O20">
+        <v>413</v>
+      </c>
+      <c r="P20" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="Q20" s="2">
+        <v>0.16900000000000001</v>
+      </c>
+      <c r="R20" s="2">
+        <v>0.27229999999999999</v>
+      </c>
+      <c r="S20" s="2">
+        <v>0.54830000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B20">
+      <c r="B21">
         <v>143</v>
       </c>
-      <c r="C20" s="5">
+      <c r="C21" s="5">
         <v>411</v>
       </c>
-      <c r="D20" s="5">
+      <c r="D21" s="5">
         <v>86</v>
       </c>
-      <c r="E20">
+      <c r="E21">
         <v>354</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F21" s="2">
         <v>0.62439999999999996</v>
       </c>
-      <c r="G20" s="2">
+      <c r="G21" s="2">
         <v>0.28770000000000001</v>
       </c>
-      <c r="H20" s="2">
+      <c r="H21" s="2">
         <v>0.39389999999999997</v>
       </c>
-      <c r="I20" s="2">
+      <c r="I21" s="2">
         <v>0.55730000000000002</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="K21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="L20">
+      <c r="L21">
         <v>113</v>
       </c>
-      <c r="M20" s="5">
+      <c r="M21" s="5">
         <v>468</v>
       </c>
-      <c r="N20" s="5">
+      <c r="N21" s="5">
         <v>29</v>
       </c>
-      <c r="O20">
+      <c r="O21">
         <v>384</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P21" s="2">
         <v>0.79579999999999995</v>
       </c>
-      <c r="Q20" s="2">
+      <c r="Q21" s="2">
         <v>0.22739999999999999</v>
       </c>
-      <c r="R20" s="2">
+      <c r="R21" s="2">
         <v>0.35370000000000001</v>
       </c>
-      <c r="S20" s="2">
+      <c r="S21" s="2">
         <v>0.58450000000000002</v>
-      </c>
-    </row>
-    <row r="21" spans="1:19" ht="39" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="10">
-        <v>161</v>
-      </c>
-      <c r="C21">
-        <v>382</v>
-      </c>
-      <c r="D21">
-        <v>115</v>
-      </c>
-      <c r="E21">
-        <v>336</v>
-      </c>
-      <c r="F21" s="8">
-        <v>0.58330000000000004</v>
-      </c>
-      <c r="G21" s="8">
-        <v>0.32390000000000002</v>
-      </c>
-      <c r="H21" s="8">
-        <v>0.41660000000000003</v>
-      </c>
-      <c r="I21" s="8">
-        <v>0.54630000000000001</v>
-      </c>
-      <c r="K21" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L21" s="10">
-        <v>157</v>
-      </c>
-      <c r="M21">
-        <v>441</v>
-      </c>
-      <c r="N21">
-        <v>56</v>
-      </c>
-      <c r="O21">
-        <v>340</v>
-      </c>
-      <c r="P21" s="8">
-        <v>0.73709999999999998</v>
-      </c>
-      <c r="Q21" s="8">
-        <v>0.31590000000000001</v>
-      </c>
-      <c r="R21" s="8">
-        <v>0.44230000000000003</v>
-      </c>
-      <c r="S21" s="8">
-        <v>0.60160000000000002</v>
       </c>
     </row>
     <row r="22" spans="1:19" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="10">
+        <v>161</v>
+      </c>
+      <c r="C22">
+        <v>382</v>
+      </c>
+      <c r="D22">
+        <v>115</v>
+      </c>
+      <c r="E22">
+        <v>336</v>
+      </c>
+      <c r="F22" s="8">
+        <v>0.58330000000000004</v>
+      </c>
+      <c r="G22" s="8">
+        <v>0.32390000000000002</v>
+      </c>
+      <c r="H22" s="8">
+        <v>0.41660000000000003</v>
+      </c>
+      <c r="I22" s="8">
+        <v>0.54630000000000001</v>
+      </c>
+      <c r="K22" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="10">
+        <v>157</v>
+      </c>
+      <c r="M22">
+        <v>441</v>
+      </c>
+      <c r="N22">
+        <v>56</v>
+      </c>
+      <c r="O22">
+        <v>340</v>
+      </c>
+      <c r="P22" s="8">
+        <v>0.73709999999999998</v>
+      </c>
+      <c r="Q22" s="8">
+        <v>0.31590000000000001</v>
+      </c>
+      <c r="R22" s="8">
+        <v>0.44230000000000003</v>
+      </c>
+      <c r="S22" s="8">
+        <v>0.60160000000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" ht="39" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B22" s="7">
+      <c r="B23" s="7">
         <v>326</v>
       </c>
-      <c r="C22" s="7">
+      <c r="C23" s="7">
         <v>219</v>
       </c>
-      <c r="D22" s="7">
+      <c r="D23" s="7">
         <v>278</v>
       </c>
-      <c r="E22" s="7">
+      <c r="E23" s="7">
         <v>171</v>
       </c>
-      <c r="F22" s="8">
+      <c r="F23" s="8">
         <v>0.53969999999999996</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G23" s="8">
         <v>0.65590000000000004</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H23" s="8">
         <v>0.59219999999999995</v>
       </c>
-      <c r="I22" s="8">
+      <c r="I23" s="8">
         <v>0.54830000000000001</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="K23" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="L22" s="7">
+      <c r="L23" s="7">
         <v>181</v>
       </c>
-      <c r="M22" s="7">
+      <c r="M23" s="7">
         <v>352</v>
       </c>
-      <c r="N22" s="7">
+      <c r="N23" s="7">
         <v>145</v>
       </c>
-      <c r="O22" s="7">
+      <c r="O23" s="7">
         <v>316</v>
       </c>
-      <c r="P22" s="8">
+      <c r="P23" s="8">
         <v>0.55520000000000003</v>
       </c>
-      <c r="Q22" s="8">
+      <c r="Q23" s="8">
         <v>0.36420000000000002</v>
       </c>
-      <c r="R22" s="8">
+      <c r="R23" s="8">
         <v>0.43990000000000001</v>
       </c>
-      <c r="S22" s="8">
+      <c r="S23" s="8">
         <v>0.53620000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="11" t="s">
+    <row r="24" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B24" s="5">
         <v>354</v>
       </c>
-      <c r="C23">
+      <c r="C24">
         <v>244</v>
       </c>
-      <c r="D23">
+      <c r="D24">
         <v>253</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E24" s="5">
         <v>143</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F24" s="6">
         <v>0.58320000000000005</v>
       </c>
-      <c r="G23" s="6">
+      <c r="G24" s="6">
         <v>0.71230000000000004</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H24" s="6">
         <v>0.6431</v>
       </c>
-      <c r="I23" s="6">
+      <c r="I24" s="6">
         <v>0.60160000000000002</v>
       </c>
-      <c r="K23" s="9" t="s">
+      <c r="K24" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="L23" s="5">
+      <c r="L24" s="5">
         <v>226</v>
       </c>
-      <c r="M23" s="7">
+      <c r="M24" s="7">
         <v>443</v>
       </c>
-      <c r="N23" s="7">
+      <c r="N24" s="7">
         <v>54</v>
       </c>
-      <c r="O23" s="5">
+      <c r="O24" s="5">
         <v>271</v>
       </c>
-      <c r="P23" s="6">
+      <c r="P24" s="6">
         <v>0.80810000000000004</v>
       </c>
-      <c r="Q23" s="6">
+      <c r="Q24" s="6">
         <v>0.45739999999999997</v>
       </c>
-      <c r="R23" s="6">
+      <c r="R24" s="6">
         <v>0.58169999999999999</v>
       </c>
-      <c r="S23" s="6">
+      <c r="S24" s="6">
         <v>0.67300000000000004</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A26" s="12" t="s">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A27" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
-      <c r="I26" s="3"/>
-      <c r="K26" s="12" t="s">
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="K27" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="L26" s="12"/>
-      <c r="M26" s="12"/>
-      <c r="N26" s="12"/>
-      <c r="O26" s="12"/>
-      <c r="P26" s="12"/>
-      <c r="Q26" s="12"/>
-      <c r="R26" s="12"/>
-      <c r="S26" s="3"/>
-    </row>
-    <row r="27" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" t="s">
-        <v>1</v>
-      </c>
-      <c r="C27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D27" t="s">
-        <v>3</v>
-      </c>
-      <c r="E27" t="s">
-        <v>4</v>
-      </c>
-      <c r="F27" t="s">
-        <v>8</v>
-      </c>
-      <c r="G27" t="s">
-        <v>9</v>
-      </c>
-      <c r="H27" t="s">
-        <v>10</v>
-      </c>
-      <c r="I27" t="s">
-        <v>11</v>
-      </c>
-      <c r="K27" t="s">
-        <v>27</v>
-      </c>
-      <c r="L27" t="s">
-        <v>1</v>
-      </c>
-      <c r="M27" t="s">
-        <v>2</v>
-      </c>
-      <c r="N27" t="s">
-        <v>3</v>
-      </c>
-      <c r="O27" t="s">
-        <v>4</v>
-      </c>
-      <c r="P27" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>9</v>
-      </c>
-      <c r="R27" t="s">
-        <v>10</v>
-      </c>
-      <c r="S27" t="s">
-        <v>11</v>
-      </c>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
     </row>
     <row r="28" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B28">
-        <v>354</v>
-      </c>
-      <c r="C28">
-        <v>244</v>
-      </c>
-      <c r="D28">
-        <v>253</v>
-      </c>
-      <c r="E28">
-        <v>143</v>
-      </c>
-      <c r="F28" s="2">
-        <v>0.58320000000000005</v>
-      </c>
-      <c r="G28" s="2">
-        <v>0.71230000000000004</v>
-      </c>
-      <c r="H28" s="2">
-        <v>0.6431</v>
-      </c>
-      <c r="I28" s="2">
-        <v>0.60160000000000002</v>
-      </c>
-      <c r="K28" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="L28" s="7">
-        <v>226</v>
-      </c>
-      <c r="M28" s="7">
-        <v>443</v>
-      </c>
-      <c r="N28" s="7">
-        <v>54</v>
-      </c>
-      <c r="O28" s="7">
-        <v>271</v>
-      </c>
-      <c r="P28" s="8">
-        <v>0.80810000000000004</v>
-      </c>
-      <c r="Q28" s="8">
-        <v>0.45739999999999997</v>
-      </c>
-      <c r="R28" s="8">
-        <v>0.58169999999999999</v>
-      </c>
-      <c r="S28" s="8">
-        <v>0.67300000000000004</v>
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" t="s">
+        <v>4</v>
+      </c>
+      <c r="F28" t="s">
+        <v>8</v>
+      </c>
+      <c r="G28" t="s">
+        <v>9</v>
+      </c>
+      <c r="H28" t="s">
+        <v>10</v>
+      </c>
+      <c r="I28" t="s">
+        <v>11</v>
+      </c>
+      <c r="K28" t="s">
+        <v>27</v>
+      </c>
+      <c r="L28" t="s">
+        <v>1</v>
+      </c>
+      <c r="M28" t="s">
+        <v>2</v>
+      </c>
+      <c r="N28" t="s">
+        <v>3</v>
+      </c>
+      <c r="O28" t="s">
+        <v>4</v>
+      </c>
+      <c r="P28" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>9</v>
+      </c>
+      <c r="R28" t="s">
+        <v>10</v>
+      </c>
+      <c r="S28" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29">
-        <v>536</v>
+        <v>354</v>
       </c>
       <c r="C29">
-        <v>483</v>
+        <v>244</v>
       </c>
       <c r="D29">
-        <v>513</v>
+        <v>253</v>
       </c>
       <c r="E29">
-        <v>460</v>
+        <v>143</v>
       </c>
       <c r="F29" s="2">
-        <v>0.51100000000000001</v>
+        <v>0.58320000000000005</v>
       </c>
       <c r="G29" s="2">
-        <v>0.53820000000000001</v>
+        <v>0.71230000000000004</v>
       </c>
       <c r="H29" s="2">
-        <v>0.5242</v>
+        <v>0.6431</v>
       </c>
       <c r="I29" s="2">
-        <v>0.51149999999999995</v>
+        <v>0.60160000000000002</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="L29">
-        <v>386</v>
-      </c>
-      <c r="M29">
-        <v>891</v>
-      </c>
-      <c r="N29">
-        <v>105</v>
-      </c>
-      <c r="O29">
-        <v>610</v>
-      </c>
-      <c r="P29" s="2">
-        <v>0.78620000000000001</v>
-      </c>
-      <c r="Q29" s="2">
-        <v>0.3876</v>
-      </c>
-      <c r="R29" s="2">
-        <v>0.51919999999999999</v>
-      </c>
-      <c r="S29" s="2">
-        <v>0.6411</v>
+        <v>28</v>
+      </c>
+      <c r="L29" s="7">
+        <v>226</v>
+      </c>
+      <c r="M29" s="7">
+        <v>443</v>
+      </c>
+      <c r="N29" s="7">
+        <v>54</v>
+      </c>
+      <c r="O29" s="7">
+        <v>271</v>
+      </c>
+      <c r="P29" s="8">
+        <v>0.80810000000000004</v>
+      </c>
+      <c r="Q29" s="8">
+        <v>0.45739999999999997</v>
+      </c>
+      <c r="R29" s="8">
+        <v>0.58169999999999999</v>
+      </c>
+      <c r="S29" s="8">
+        <v>0.67300000000000004</v>
       </c>
     </row>
     <row r="30" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30">
+        <v>536</v>
+      </c>
+      <c r="C30">
+        <v>483</v>
+      </c>
+      <c r="D30">
+        <v>513</v>
+      </c>
+      <c r="E30">
+        <v>460</v>
+      </c>
+      <c r="F30" s="2">
+        <v>0.51100000000000001</v>
+      </c>
+      <c r="G30" s="2">
+        <v>0.53820000000000001</v>
+      </c>
+      <c r="H30" s="2">
+        <v>0.5242</v>
+      </c>
+      <c r="I30" s="2">
+        <v>0.51149999999999995</v>
+      </c>
+      <c r="K30" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L30">
+        <v>386</v>
+      </c>
+      <c r="M30">
+        <v>891</v>
+      </c>
+      <c r="N30">
+        <v>105</v>
+      </c>
+      <c r="O30">
+        <v>610</v>
+      </c>
+      <c r="P30" s="2">
+        <v>0.78620000000000001</v>
+      </c>
+      <c r="Q30" s="2">
+        <v>0.3876</v>
+      </c>
+      <c r="R30" s="2">
+        <v>0.51919999999999999</v>
+      </c>
+      <c r="S30" s="2">
+        <v>0.6411</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B31" s="10">
         <v>85</v>
       </c>
-      <c r="C30">
+      <c r="C31">
         <v>39</v>
       </c>
-      <c r="D30">
+      <c r="D31">
         <v>66</v>
       </c>
-      <c r="E30">
+      <c r="E31">
         <v>20</v>
       </c>
-      <c r="F30" s="8">
+      <c r="F31" s="8">
         <v>0.56289999999999996</v>
       </c>
-      <c r="G30" s="8">
+      <c r="G31" s="8">
         <v>0.8095</v>
       </c>
-      <c r="H30" s="8">
+      <c r="H31" s="8">
         <v>0.66410000000000002</v>
       </c>
-      <c r="I30" s="8">
+      <c r="I31" s="8">
         <v>0.59050000000000002</v>
       </c>
-      <c r="K30" s="9" t="s">
+      <c r="K31" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="L30" s="10">
+      <c r="L31" s="10">
         <v>42</v>
       </c>
-      <c r="M30">
+      <c r="M31">
         <v>93</v>
       </c>
-      <c r="N30">
+      <c r="N31">
         <v>12</v>
       </c>
-      <c r="O30">
+      <c r="O31">
         <v>63</v>
       </c>
-      <c r="P30" s="8">
+      <c r="P31" s="8">
         <v>0.77780000000000005</v>
       </c>
-      <c r="Q30" s="8">
+      <c r="Q31" s="8">
         <v>0.4</v>
       </c>
-      <c r="R30" s="8">
+      <c r="R31" s="8">
         <v>0.52829999999999999</v>
       </c>
-      <c r="S30" s="8">
+      <c r="S31" s="8">
         <v>0.64290000000000003</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="A26:H26"/>
-    <mergeCell ref="K17:S17"/>
-    <mergeCell ref="K26:R26"/>
+    <mergeCell ref="A27:I27"/>
+    <mergeCell ref="K27:S27"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="K1:S1"/>
-    <mergeCell ref="A8:H8"/>
-    <mergeCell ref="K8:S8"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="K9:S9"/>
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="K18:S18"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Supplementary_Materials/detection_tptnfpfn.xlsx
+++ b/Supplementary_Materials/detection_tptnfpfn.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\OneDrive\Desktop\Supplementary_Materials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F399CAA9-635A-4200-9BF3-0F71829D712B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80D0CE1F-E5BA-46F9-ABBA-15DA2A8A7AC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,24 +28,16 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="95">
   <si>
     <t>Model</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>TN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FP</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>FN</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -183,6 +175,238 @@
   </si>
   <si>
     <t>P-R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TP/TPR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FP/FPR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>366/73.64%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>243/48.89%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>306/61.57%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>247/49.70%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>354/71.23%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>253/50.91%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>368/74.04%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>264/53.12%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>158/31.79</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>39/7.85%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>147/29.58%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>61/12.27%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>226/45.47%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>54/10.87%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>52/10.46%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>138/27.77%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>144/28.97%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>130/26.16%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>90/18.11%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>117/23.54%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>76/15.29%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>114/22.94%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>88/17.71%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>84/16.90%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>96/19.32%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>137/27.57%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>59/11.87%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>129/25.96%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>71/14.29%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24/4.83</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>244/49.90%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>226/49.90%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>54/10.46%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>126/25.35%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>98/19.72%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>143/28.77%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>86/17.30%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>161/32.39%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>115/23.14%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>326/65.59%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>278/55.94%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>36/7.24%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>113/22.74%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>29/5.84%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>157/31.59%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>56/11.27%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>181/36.42%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>145/29.18%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>536/53.82%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>513/51.51%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>85/80.96%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>66/13.28%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>386/38.76%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>105/10.54%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>42/40.00%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12/11.43%</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -324,9 +548,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -338,11 +559,240 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="14">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFDEE0E3"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE0E3"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE0E3"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE0E3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFDEE0E3"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFDEE0E3"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE0E3"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE0E3"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE0E3"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFDEE0E3"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE0E3"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE0E3"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE0E3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="medium">
+          <color rgb="FFDEE0E3"/>
+        </left>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFDEE0E3"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE0E3"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE0E3"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE0E3"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFDEE0E3"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE0E3"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE0E3"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE0E3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="等线"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="medium">
+          <color rgb="FFDEE0E3"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFDEE0E3"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFDEE0E3"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFDEE0E3"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
@@ -373,160 +823,6 @@
         <charset val="134"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFDEE0E3"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE0E3"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE0E3"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE0E3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color rgb="FFDEE0E3"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFDEE0E3"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE0E3"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE0E3"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE0E3"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFDEE0E3"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE0E3"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE0E3"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE0E3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="medium">
-          <color rgb="FFDEE0E3"/>
-        </left>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFDEE0E3"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE0E3"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE0E3"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE0E3"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="medium">
@@ -581,78 +877,6 @@
         <horizontal/>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFDEE0E3"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE0E3"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE0E3"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE0E3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <name val="等线"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="medium">
-          <color rgb="FFDEE0E3"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFDEE0E3"/>
-        </right>
-        <top style="medium">
-          <color rgb="FFDEE0E3"/>
-        </top>
-        <bottom style="medium">
-          <color rgb="FFDEE0E3"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -671,9 +895,9 @@
   <autoFilter ref="A2:I6" xr:uid="{88CA140E-7B21-49D9-8C53-10532143A179}"/>
   <tableColumns count="9">
     <tableColumn id="1" xr3:uid="{3599CD0A-29F7-40B5-B678-FB9EDF2364EC}" name="Model" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{5AC6376B-5EB3-47BC-8586-471E1888F0C7}" name="TP"/>
+    <tableColumn id="2" xr3:uid="{5AC6376B-5EB3-47BC-8586-471E1888F0C7}" name="TP/TPR"/>
     <tableColumn id="3" xr3:uid="{12E9AFF4-C7A8-442C-BF37-D729453435FE}" name="TN"/>
-    <tableColumn id="4" xr3:uid="{DE35441A-AF6F-4F39-8388-C0898A4C0F33}" name="FP"/>
+    <tableColumn id="4" xr3:uid="{DE35441A-AF6F-4F39-8388-C0898A4C0F33}" name="FP/FPR"/>
     <tableColumn id="5" xr3:uid="{51566BE9-7D23-4520-AF65-36C6137F5237}" name="FN"/>
     <tableColumn id="6" xr3:uid="{B12309FB-8DFB-4341-952A-AE3ACD987FE2}" name="Precision"/>
     <tableColumn id="7" xr3:uid="{C462A323-E3F3-473F-A277-69EC02FB8CCC}" name="Recall"/>
@@ -689,18 +913,18 @@
   <autoFilter ref="K2:W6" xr:uid="{155D92FD-02B0-407A-9C5C-CFD33AEA1E73}"/>
   <tableColumns count="13">
     <tableColumn id="1" xr3:uid="{0EB1CB38-3798-4740-AD37-70798E871088}" name="Model" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{7CDE3FC9-CCBA-4685-904D-3E0F06E89C38}" name="TP"/>
+    <tableColumn id="2" xr3:uid="{7CDE3FC9-CCBA-4685-904D-3E0F06E89C38}" name="TP/TPR"/>
     <tableColumn id="3" xr3:uid="{FD330268-3D03-44B1-B6D2-CB2974EDD466}" name="TN"/>
-    <tableColumn id="4" xr3:uid="{8491126D-16AA-42E9-AACE-BAB8B212BA34}" name="FP"/>
+    <tableColumn id="4" xr3:uid="{8491126D-16AA-42E9-AACE-BAB8B212BA34}" name="FP/FPR"/>
     <tableColumn id="5" xr3:uid="{D4C47E13-82EE-4D6C-9228-98BBE62499C5}" name="FN"/>
     <tableColumn id="6" xr3:uid="{FE0899C7-C921-40AF-B6EE-3EB9D2E6F615}" name="Precision"/>
     <tableColumn id="7" xr3:uid="{2A9F603B-4B2B-441E-8F96-C0E64D8B280C}" name="Recall"/>
     <tableColumn id="8" xr3:uid="{D8BB11E1-7308-4242-BAD5-7E7F1F044262}" name="F1"/>
     <tableColumn id="9" xr3:uid="{FB0A8A80-B453-45D8-B4CD-DC9D7C6D7780}" name="Accuracy"/>
-    <tableColumn id="10" xr3:uid="{38F6E6FC-19A4-4540-A065-9BFE82F155D5}" name="P-C" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{3431DAF4-954A-439A-B129-16A7B9149092}" name="P-V" dataDxfId="2"/>
-    <tableColumn id="13" xr3:uid="{A5012397-4054-4842-B30D-1782BE044013}" name="P-B" dataDxfId="1"/>
-    <tableColumn id="14" xr3:uid="{0F284BB8-79F8-4595-8326-90B7D4DDFD31}" name="P-R" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{38F6E6FC-19A4-4540-A065-9BFE82F155D5}" name="P-C" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{3431DAF4-954A-439A-B129-16A7B9149092}" name="P-V" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{A5012397-4054-4842-B30D-1782BE044013}" name="P-B" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{0F284BB8-79F8-4595-8326-90B7D4DDFD31}" name="P-R" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -710,10 +934,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{81F1B3FD-B3DD-428D-B811-6E96F15E653C}" name="表2_5" displayName="表2_5" ref="A10:I15" totalsRowShown="0">
   <autoFilter ref="A10:I15" xr:uid="{81F1B3FD-B3DD-428D-B811-6E96F15E653C}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{C408C6B2-77A7-4CCF-B296-67DAACCBE024}" name="Method" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{6AAC990C-7814-4010-BB7C-BE84EFC80B96}" name="TP"/>
+    <tableColumn id="1" xr3:uid="{C408C6B2-77A7-4CCF-B296-67DAACCBE024}" name="Method" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{6AAC990C-7814-4010-BB7C-BE84EFC80B96}" name="TP/TPR"/>
     <tableColumn id="3" xr3:uid="{D244E047-F1AA-441B-A547-BED64B38EEC2}" name="TN"/>
-    <tableColumn id="4" xr3:uid="{52F33817-11DB-4561-BACE-EB0B2E9D71AA}" name="FP"/>
+    <tableColumn id="4" xr3:uid="{52F33817-11DB-4561-BACE-EB0B2E9D71AA}" name="FP/FPR"/>
     <tableColumn id="5" xr3:uid="{1DBED256-F5F3-46D1-AC16-D604A130C35D}" name="FN"/>
     <tableColumn id="6" xr3:uid="{04CFD7D6-976A-4C34-AE82-2CFFA7FAA1DD}" name="Precision"/>
     <tableColumn id="7" xr3:uid="{0DEC51F0-8ACD-4C18-9E41-378017AC0554}" name="Recall"/>
@@ -728,10 +952,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{ED1EDC30-AEF7-4AEC-A90A-83EADE6E72F5}" name="表2_57" displayName="表2_57" ref="K10:S15" totalsRowShown="0">
   <autoFilter ref="K10:S15" xr:uid="{ED1EDC30-AEF7-4AEC-A90A-83EADE6E72F5}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{9FA1EFE9-0573-42A3-87DC-58163D885660}" name="Method" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{21010D3A-A70D-46B3-BE1B-4EEC4575F824}" name="TP"/>
+    <tableColumn id="1" xr3:uid="{9FA1EFE9-0573-42A3-87DC-58163D885660}" name="Method" dataDxfId="6"/>
+    <tableColumn id="2" xr3:uid="{21010D3A-A70D-46B3-BE1B-4EEC4575F824}" name="TP/TPR"/>
     <tableColumn id="3" xr3:uid="{6B91F050-B52B-4957-BE4B-2F25B524D6FD}" name="TN"/>
-    <tableColumn id="4" xr3:uid="{44C9D43F-9A4A-4271-8E38-658108C43E5A}" name="FP"/>
+    <tableColumn id="4" xr3:uid="{44C9D43F-9A4A-4271-8E38-658108C43E5A}" name="FP/FPR"/>
     <tableColumn id="5" xr3:uid="{B662CD78-BD93-4CAC-8315-E6FCD31B1131}" name="FN"/>
     <tableColumn id="6" xr3:uid="{28B1C5E0-E2D8-4A9D-8E4C-5F0351F3559A}" name="Precision"/>
     <tableColumn id="7" xr3:uid="{F37FE164-52AC-48D8-BB2C-E6CB57CCC45C}" name="Recall"/>
@@ -746,10 +970,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="8" xr:uid="{4A47D4AF-C1F4-4B2E-84E2-C1BE29BA7CC4}" name="表2_59" displayName="表2_59" ref="A19:I24" totalsRowShown="0">
   <autoFilter ref="A19:I24" xr:uid="{4A47D4AF-C1F4-4B2E-84E2-C1BE29BA7CC4}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{BCF58236-26AE-40C9-9599-9A59EC7450B2}" name="ID" dataDxfId="9"/>
-    <tableColumn id="2" xr3:uid="{CF45B29B-BE5A-4FDA-8803-A8923237A0F0}" name="TP" dataDxfId="8"/>
+    <tableColumn id="1" xr3:uid="{BCF58236-26AE-40C9-9599-9A59EC7450B2}" name="ID" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{CF45B29B-BE5A-4FDA-8803-A8923237A0F0}" name="TP/TPR" dataDxfId="4"/>
     <tableColumn id="3" xr3:uid="{F54E13CD-EBFC-4829-A77E-8E1C7890803D}" name="TN"/>
-    <tableColumn id="4" xr3:uid="{F759BB32-5E40-40A9-A0B9-89FF3B4FF21C}" name="FP"/>
+    <tableColumn id="4" xr3:uid="{F759BB32-5E40-40A9-A0B9-89FF3B4FF21C}" name="FP/FPR"/>
     <tableColumn id="5" xr3:uid="{73042ED4-CE53-4E99-B6AF-9BD2999205C5}" name="FN"/>
     <tableColumn id="6" xr3:uid="{F43BFB5B-20F6-4C59-84C1-22AD5D2B62C8}" name="Precision"/>
     <tableColumn id="7" xr3:uid="{00F69F4F-47FE-42BB-8880-7AA61DD2DA49}" name="Recall"/>
@@ -764,10 +988,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="9" xr:uid="{D9F59797-4543-40C3-956A-134AD5BD8027}" name="表9" displayName="表9" ref="A28:I31" totalsRowShown="0">
   <autoFilter ref="A28:I31" xr:uid="{D9F59797-4543-40C3-956A-134AD5BD8027}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{2E1F777C-801F-427C-9438-9D669CB2CC5F}" name="Dataset" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{2996D0E9-0986-4099-A9E6-4829F00A64A6}" name="TP"/>
+    <tableColumn id="1" xr3:uid="{2E1F777C-801F-427C-9438-9D669CB2CC5F}" name="Dataset" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{2996D0E9-0986-4099-A9E6-4829F00A64A6}" name="TP/TPR"/>
     <tableColumn id="3" xr3:uid="{A9DA785A-2CFA-4A90-924D-3B371F83F26B}" name="TN"/>
-    <tableColumn id="4" xr3:uid="{6C096669-A4B5-4BE8-B8F4-FFB7ABF2C8C6}" name="FP"/>
+    <tableColumn id="4" xr3:uid="{6C096669-A4B5-4BE8-B8F4-FFB7ABF2C8C6}" name="FP/FPR"/>
     <tableColumn id="5" xr3:uid="{C2EE662D-E356-41F3-9BC4-D531088C9A3E}" name="FN"/>
     <tableColumn id="6" xr3:uid="{A12C0EA7-0412-44A6-AC2F-548962F295FA}" name="Precision"/>
     <tableColumn id="7" xr3:uid="{FD5235FA-4D59-4988-98D9-B40DD7876FAA}" name="Recall"/>
@@ -782,10 +1006,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{E45B7DE5-6884-4AAB-B0E8-948C8ECAE034}" name="表2_5911" displayName="表2_5911" ref="K19:S24" totalsRowShown="0">
   <autoFilter ref="K19:S24" xr:uid="{E45B7DE5-6884-4AAB-B0E8-948C8ECAE034}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{8CF70A89-BE48-4C01-9D7E-FDD1454C61A5}" name="ID" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{25C65B6D-EA69-4471-81D4-43E1464B9339}" name="TP" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{8CF70A89-BE48-4C01-9D7E-FDD1454C61A5}" name="ID" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{25C65B6D-EA69-4471-81D4-43E1464B9339}" name="TP/TPR" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{1AC6B611-57E5-41B0-B363-BB9D2A11A53A}" name="TN"/>
-    <tableColumn id="4" xr3:uid="{53A506B5-237A-4F73-9FFB-FC1053E0DCBD}" name="FP"/>
+    <tableColumn id="4" xr3:uid="{53A506B5-237A-4F73-9FFB-FC1053E0DCBD}" name="FP/FPR"/>
     <tableColumn id="5" xr3:uid="{C0693F33-0CFC-4212-AB5F-B454ADBE77DD}" name="FN"/>
     <tableColumn id="6" xr3:uid="{87F5CF2C-BC2F-402D-B433-AA3A5A03733E}" name="Precision"/>
     <tableColumn id="7" xr3:uid="{E2DBA657-B141-45FF-94E8-2C562D73969A}" name="Recall"/>
@@ -800,10 +1024,10 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="11" xr:uid="{AFCC0346-4AFC-429E-87BD-CA9C9458A5B9}" name="表9_12" displayName="表9_12" ref="K28:S31" totalsRowShown="0">
   <autoFilter ref="K28:S31" xr:uid="{AFCC0346-4AFC-429E-87BD-CA9C9458A5B9}"/>
   <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{F9DAA578-1F1C-4469-BD21-048F1801D7B7}" name="Dataset" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{6FB60BB2-0755-491E-933F-23FEDF9286B8}" name="TP"/>
+    <tableColumn id="1" xr3:uid="{F9DAA578-1F1C-4469-BD21-048F1801D7B7}" name="Dataset" dataDxfId="0"/>
+    <tableColumn id="2" xr3:uid="{6FB60BB2-0755-491E-933F-23FEDF9286B8}" name="TP/TPR"/>
     <tableColumn id="3" xr3:uid="{B25EE914-F2EE-443B-85F9-3D87F49A2A92}" name="TN"/>
-    <tableColumn id="4" xr3:uid="{4C8FF114-96A0-4D3A-955A-FEBF9B2E5619}" name="FP"/>
+    <tableColumn id="4" xr3:uid="{4C8FF114-96A0-4D3A-955A-FEBF9B2E5619}" name="FP/FPR"/>
     <tableColumn id="5" xr3:uid="{2CD07B20-D0FD-43B6-AAE0-96179743F720}" name="FN"/>
     <tableColumn id="6" xr3:uid="{42AC4BF7-816C-454F-99F1-13533EA1FE35}" name="Precision"/>
     <tableColumn id="7" xr3:uid="{514DF78A-46D7-46B5-9FBA-175210519A68}" name="Recall"/>
@@ -1087,109 +1311,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
+      <c r="A1" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
       <c r="I1" s="3"/>
-      <c r="K1" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
+      <c r="K1" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="L1" s="19"/>
+      <c r="M1" s="19"/>
+      <c r="N1" s="19"/>
+      <c r="O1" s="19"/>
+      <c r="P1" s="19"/>
+      <c r="Q1" s="19"/>
+      <c r="R1" s="19"/>
+      <c r="S1" s="19"/>
     </row>
     <row r="2" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" t="s">
         <v>2</v>
       </c>
-      <c r="D2" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" t="s">
-        <v>4</v>
-      </c>
       <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>9</v>
-      </c>
-      <c r="H2" t="s">
-        <v>10</v>
-      </c>
-      <c r="I2" t="s">
-        <v>11</v>
       </c>
       <c r="K2" t="s">
         <v>0</v>
       </c>
       <c r="L2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M2" t="s">
         <v>1</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O2" t="s">
         <v>2</v>
       </c>
-      <c r="N2" t="s">
-        <v>3</v>
-      </c>
-      <c r="O2" t="s">
-        <v>4</v>
-      </c>
       <c r="P2" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>7</v>
+      </c>
+      <c r="R2" t="s">
         <v>8</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>9</v>
       </c>
-      <c r="R2" t="s">
-        <v>10</v>
-      </c>
-      <c r="S2" t="s">
-        <v>11</v>
-      </c>
       <c r="T2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U2" t="s">
+        <v>34</v>
+      </c>
+      <c r="V2" t="s">
         <v>35</v>
       </c>
-      <c r="U2" t="s">
+      <c r="W2" t="s">
         <v>36</v>
-      </c>
-      <c r="V2" t="s">
-        <v>37</v>
-      </c>
-      <c r="W2" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="5">
-        <v>366</v>
+        <v>5</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="C3" s="5">
         <v>254</v>
       </c>
-      <c r="D3" s="5">
-        <v>243</v>
+      <c r="D3" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="E3" s="5">
         <v>131</v>
@@ -1207,16 +1431,16 @@
         <v>0.61950000000000005</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L3">
-        <v>158</v>
+        <v>5</v>
+      </c>
+      <c r="L3" t="s">
+        <v>47</v>
       </c>
       <c r="M3" s="5">
         <v>458</v>
       </c>
-      <c r="N3" s="5">
-        <v>39</v>
+      <c r="N3" s="5" t="s">
+        <v>48</v>
       </c>
       <c r="O3">
         <v>339</v>
@@ -1248,16 +1472,16 @@
     </row>
     <row r="4" spans="1:23" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>306</v>
+        <v>4</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
       </c>
       <c r="C4">
         <v>250</v>
       </c>
-      <c r="D4">
-        <v>247</v>
+      <c r="D4" t="s">
+        <v>42</v>
       </c>
       <c r="E4">
         <v>191</v>
@@ -1275,16 +1499,16 @@
         <v>0.55930000000000002</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="L4">
-        <v>147</v>
+        <v>4</v>
+      </c>
+      <c r="L4" t="s">
+        <v>49</v>
       </c>
       <c r="M4">
         <v>436</v>
       </c>
-      <c r="N4">
-        <v>61</v>
+      <c r="N4" t="s">
+        <v>50</v>
       </c>
       <c r="O4">
         <v>350</v>
@@ -1316,16 +1540,16 @@
     </row>
     <row r="5" spans="1:23" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5">
-        <v>354</v>
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>43</v>
       </c>
       <c r="C5">
         <v>244</v>
       </c>
-      <c r="D5">
-        <v>253</v>
+      <c r="D5" t="s">
+        <v>44</v>
       </c>
       <c r="E5">
         <v>143</v>
@@ -1343,16 +1567,16 @@
         <v>0.60160000000000002</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L5" s="7">
-        <v>226</v>
+        <v>3</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="M5" s="7">
         <v>443</v>
       </c>
-      <c r="N5" s="7">
-        <v>54</v>
+      <c r="N5" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="O5" s="7">
         <v>271</v>
@@ -1383,165 +1607,165 @@
       </c>
     </row>
     <row r="6" spans="1:23" ht="38.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="14">
-        <v>368</v>
-      </c>
-      <c r="C6" s="14">
+      <c r="A6" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="13">
         <v>233</v>
       </c>
-      <c r="D6" s="14">
-        <v>264</v>
-      </c>
-      <c r="E6" s="14">
+      <c r="D6" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="E6" s="13">
         <v>129</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="14">
         <v>0.58220000000000005</v>
       </c>
-      <c r="G6" s="15">
+      <c r="G6" s="14">
         <v>0.74039999999999995</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="14">
         <v>0.65190000000000003</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="14">
         <v>0.60460000000000003</v>
       </c>
-      <c r="K6" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="L6" s="17">
-        <v>244</v>
-      </c>
-      <c r="M6" s="14">
+      <c r="K6" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M6" s="13">
         <v>445</v>
       </c>
-      <c r="N6" s="19">
-        <v>52</v>
-      </c>
-      <c r="O6" s="17">
+      <c r="N6" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="O6" s="16">
         <v>253</v>
       </c>
-      <c r="P6" s="18">
+      <c r="P6" s="17">
         <v>0.82430000000000003</v>
       </c>
-      <c r="Q6" s="18">
+      <c r="Q6" s="17">
         <v>0.4909</v>
       </c>
-      <c r="R6" s="18">
+      <c r="R6" s="17">
         <v>0.61539999999999995</v>
       </c>
-      <c r="S6" s="18">
+      <c r="S6" s="17">
         <v>0.69320000000000004</v>
       </c>
-      <c r="T6" s="18">
+      <c r="T6" s="17">
         <v>0.39400000000000002</v>
       </c>
-      <c r="U6" s="15">
+      <c r="U6" s="14">
         <v>9.7000000000000003E-2</v>
       </c>
-      <c r="V6" s="18">
+      <c r="V6" s="17">
         <v>0.501</v>
       </c>
-      <c r="W6" s="18">
+      <c r="W6" s="17">
         <v>8.0000000000000002E-3</v>
       </c>
     </row>
     <row r="9" spans="1:23" x14ac:dyDescent="0.2">
-      <c r="A9" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
-      <c r="D9" s="12"/>
-      <c r="E9" s="12"/>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
+      <c r="A9" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
       <c r="I9" s="3"/>
-      <c r="K9" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" s="12"/>
-      <c r="M9" s="12"/>
-      <c r="N9" s="12"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="12"/>
-      <c r="R9" s="12"/>
-      <c r="S9" s="12"/>
+      <c r="K9" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
     </row>
     <row r="10" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" t="s">
         <v>1</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
         <v>2</v>
       </c>
-      <c r="D10" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" t="s">
-        <v>4</v>
-      </c>
       <c r="F10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" t="s">
+        <v>7</v>
+      </c>
+      <c r="H10" t="s">
         <v>8</v>
       </c>
-      <c r="G10" t="s">
+      <c r="I10" t="s">
         <v>9</v>
       </c>
-      <c r="H10" t="s">
-        <v>10</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="K10" t="s">
         <v>11</v>
       </c>
-      <c r="K10" t="s">
-        <v>13</v>
-      </c>
       <c r="L10" t="s">
+        <v>37</v>
+      </c>
+      <c r="M10" t="s">
         <v>1</v>
       </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
+        <v>38</v>
+      </c>
+      <c r="O10" t="s">
         <v>2</v>
       </c>
-      <c r="N10" t="s">
-        <v>3</v>
-      </c>
-      <c r="O10" t="s">
-        <v>4</v>
-      </c>
       <c r="P10" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>7</v>
+      </c>
+      <c r="R10" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" t="s">
+      <c r="S10" t="s">
         <v>9</v>
-      </c>
-      <c r="R10" t="s">
-        <v>10</v>
-      </c>
-      <c r="S10" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="26.25" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11">
-        <v>144</v>
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>55</v>
       </c>
       <c r="C11">
         <v>359</v>
       </c>
-      <c r="D11">
-        <v>138</v>
+      <c r="D11" t="s">
+        <v>54</v>
       </c>
       <c r="E11">
         <v>353</v>
@@ -1559,16 +1783,16 @@
         <v>0.50600000000000001</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="L11">
-        <v>84</v>
+        <v>10</v>
+      </c>
+      <c r="L11" t="s">
+        <v>62</v>
       </c>
       <c r="M11">
         <v>401</v>
       </c>
-      <c r="N11">
-        <v>96</v>
+      <c r="N11" t="s">
+        <v>63</v>
       </c>
       <c r="O11">
         <v>413</v>
@@ -1588,16 +1812,16 @@
     </row>
     <row r="12" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12">
-        <v>130</v>
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>56</v>
       </c>
       <c r="C12">
         <v>407</v>
       </c>
-      <c r="D12">
-        <v>90</v>
+      <c r="D12" t="s">
+        <v>57</v>
       </c>
       <c r="E12">
         <v>367</v>
@@ -1615,16 +1839,16 @@
         <v>0.54020000000000001</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12">
-        <v>137</v>
+        <v>13</v>
+      </c>
+      <c r="L12" t="s">
+        <v>64</v>
       </c>
       <c r="M12">
         <v>438</v>
       </c>
-      <c r="N12">
-        <v>59</v>
+      <c r="N12" t="s">
+        <v>65</v>
       </c>
       <c r="O12">
         <v>360</v>
@@ -1645,16 +1869,16 @@
     </row>
     <row r="13" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="7">
-        <v>117</v>
+        <v>14</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>58</v>
       </c>
       <c r="C13" s="5">
         <v>421</v>
       </c>
-      <c r="D13" s="5">
-        <v>76</v>
+      <c r="D13" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="E13" s="7">
         <v>380</v>
@@ -1672,16 +1896,16 @@
         <v>0.54120000000000001</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="L13" s="7">
-        <v>129</v>
+        <v>14</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="M13" s="7">
         <v>407</v>
       </c>
-      <c r="N13" s="7">
-        <v>90</v>
+      <c r="N13" s="7" t="s">
+        <v>57</v>
       </c>
       <c r="O13" s="7">
         <v>368</v>
@@ -1702,16 +1926,16 @@
     </row>
     <row r="14" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="7">
-        <v>114</v>
+        <v>15</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>60</v>
       </c>
       <c r="C14" s="7">
         <v>409</v>
       </c>
-      <c r="D14" s="7">
-        <v>88</v>
+      <c r="D14" s="7" t="s">
+        <v>61</v>
       </c>
       <c r="E14" s="7">
         <v>383</v>
@@ -1729,16 +1953,16 @@
         <v>0.5262</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="L14" s="7">
-        <v>71</v>
+        <v>15</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="M14" s="5">
         <v>473</v>
       </c>
-      <c r="N14" s="5">
-        <v>24</v>
+      <c r="N14" s="5" t="s">
+        <v>68</v>
       </c>
       <c r="O14" s="7">
         <v>426</v>
@@ -1758,16 +1982,16 @@
     </row>
     <row r="15" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="5">
-        <v>354</v>
+        <v>16</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="C15">
         <v>244</v>
       </c>
-      <c r="D15">
-        <v>253</v>
+      <c r="D15" t="s">
+        <v>44</v>
       </c>
       <c r="E15" s="5">
         <v>143</v>
@@ -1785,16 +2009,16 @@
         <v>0.60160000000000002</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="L15" s="5">
-        <v>226</v>
+        <v>16</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="M15" s="7">
         <v>443</v>
       </c>
-      <c r="N15" s="7">
-        <v>54</v>
+      <c r="N15" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="O15" s="5">
         <v>271</v>
@@ -1813,97 +2037,97 @@
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A18" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="K18" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
+      <c r="A18" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="K18" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="L18" s="19"/>
+      <c r="M18" s="19"/>
+      <c r="N18" s="19"/>
+      <c r="O18" s="19"/>
+      <c r="P18" s="19"/>
+      <c r="Q18" s="19"/>
+      <c r="R18" s="19"/>
+      <c r="S18" s="19"/>
     </row>
     <row r="19" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B19" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" t="s">
         <v>1</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
+        <v>38</v>
+      </c>
+      <c r="E19" t="s">
         <v>2</v>
       </c>
-      <c r="D19" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" t="s">
-        <v>4</v>
-      </c>
       <c r="F19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" t="s">
+        <v>7</v>
+      </c>
+      <c r="H19" t="s">
         <v>8</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>9</v>
       </c>
-      <c r="H19" t="s">
-        <v>10</v>
-      </c>
-      <c r="I19" t="s">
-        <v>11</v>
-      </c>
       <c r="K19" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L19" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" t="s">
         <v>1</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
+        <v>38</v>
+      </c>
+      <c r="O19" t="s">
         <v>2</v>
       </c>
-      <c r="N19" t="s">
-        <v>3</v>
-      </c>
-      <c r="O19" t="s">
-        <v>4</v>
-      </c>
       <c r="P19" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>7</v>
+      </c>
+      <c r="R19" t="s">
         <v>8</v>
       </c>
-      <c r="Q19" t="s">
+      <c r="S19" t="s">
         <v>9</v>
-      </c>
-      <c r="R19" t="s">
-        <v>10</v>
-      </c>
-      <c r="S19" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="20" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="9">
         <v>1</v>
       </c>
-      <c r="B20">
-        <v>126</v>
+      <c r="B20" t="s">
+        <v>72</v>
       </c>
       <c r="C20">
         <v>399</v>
       </c>
-      <c r="D20">
-        <v>98</v>
+      <c r="D20" t="s">
+        <v>73</v>
       </c>
       <c r="E20">
         <v>371</v>
@@ -1923,14 +2147,14 @@
       <c r="K20" s="9">
         <v>1</v>
       </c>
-      <c r="L20">
-        <v>84</v>
+      <c r="L20" t="s">
+        <v>62</v>
       </c>
       <c r="M20">
         <v>461</v>
       </c>
-      <c r="N20">
-        <v>36</v>
+      <c r="N20" t="s">
+        <v>80</v>
       </c>
       <c r="O20">
         <v>413</v>
@@ -1950,16 +2174,16 @@
     </row>
     <row r="21" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21">
-        <v>143</v>
+        <v>22</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
       </c>
       <c r="C21" s="5">
         <v>411</v>
       </c>
-      <c r="D21" s="5">
-        <v>86</v>
+      <c r="D21" s="5" t="s">
+        <v>75</v>
       </c>
       <c r="E21">
         <v>354</v>
@@ -1977,16 +2201,16 @@
         <v>0.55730000000000002</v>
       </c>
       <c r="K21" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="L21">
-        <v>113</v>
+        <v>22</v>
+      </c>
+      <c r="L21" t="s">
+        <v>81</v>
       </c>
       <c r="M21" s="5">
         <v>468</v>
       </c>
-      <c r="N21" s="5">
-        <v>29</v>
+      <c r="N21" s="5" t="s">
+        <v>82</v>
       </c>
       <c r="O21">
         <v>384</v>
@@ -2006,16 +2230,16 @@
     </row>
     <row r="22" spans="1:19" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="10">
-        <v>161</v>
+        <v>23</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>76</v>
       </c>
       <c r="C22">
         <v>382</v>
       </c>
-      <c r="D22">
-        <v>115</v>
+      <c r="D22" t="s">
+        <v>77</v>
       </c>
       <c r="E22">
         <v>336</v>
@@ -2033,16 +2257,16 @@
         <v>0.54630000000000001</v>
       </c>
       <c r="K22" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="L22" s="10">
-        <v>157</v>
+        <v>23</v>
+      </c>
+      <c r="L22" s="10" t="s">
+        <v>83</v>
       </c>
       <c r="M22">
         <v>441</v>
       </c>
-      <c r="N22">
-        <v>56</v>
+      <c r="N22" t="s">
+        <v>84</v>
       </c>
       <c r="O22">
         <v>340</v>
@@ -2062,16 +2286,16 @@
     </row>
     <row r="23" spans="1:19" ht="39" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="7">
-        <v>326</v>
+        <v>24</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>78</v>
       </c>
       <c r="C23" s="7">
         <v>219</v>
       </c>
-      <c r="D23" s="7">
-        <v>278</v>
+      <c r="D23" s="7" t="s">
+        <v>79</v>
       </c>
       <c r="E23" s="7">
         <v>171</v>
@@ -2089,16 +2313,16 @@
         <v>0.54830000000000001</v>
       </c>
       <c r="K23" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L23" s="7">
-        <v>181</v>
+        <v>24</v>
+      </c>
+      <c r="L23" s="7" t="s">
+        <v>85</v>
       </c>
       <c r="M23" s="7">
         <v>352</v>
       </c>
-      <c r="N23" s="7">
-        <v>145</v>
+      <c r="N23" s="7" t="s">
+        <v>86</v>
       </c>
       <c r="O23" s="7">
         <v>316</v>
@@ -2118,16 +2342,16 @@
     </row>
     <row r="24" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="5">
-        <v>354</v>
+        <v>16</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>43</v>
       </c>
       <c r="C24">
         <v>244</v>
       </c>
-      <c r="D24">
-        <v>253</v>
+      <c r="D24" t="s">
+        <v>44</v>
       </c>
       <c r="E24" s="5">
         <v>143</v>
@@ -2145,16 +2369,16 @@
         <v>0.60160000000000002</v>
       </c>
       <c r="K24" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="L24" s="5">
-        <v>226</v>
+        <v>16</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>70</v>
       </c>
       <c r="M24" s="7">
         <v>443</v>
       </c>
-      <c r="N24" s="7">
-        <v>54</v>
+      <c r="N24" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="O24" s="5">
         <v>271</v>
@@ -2173,97 +2397,97 @@
       </c>
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A27" s="12" t="s">
+      <c r="A27" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="K27" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="K27" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="L27" s="12"/>
-      <c r="M27" s="12"/>
-      <c r="N27" s="12"/>
-      <c r="O27" s="12"/>
-      <c r="P27" s="12"/>
-      <c r="Q27" s="12"/>
-      <c r="R27" s="12"/>
-      <c r="S27" s="12"/>
+      <c r="L27" s="19"/>
+      <c r="M27" s="19"/>
+      <c r="N27" s="19"/>
+      <c r="O27" s="19"/>
+      <c r="P27" s="19"/>
+      <c r="Q27" s="19"/>
+      <c r="R27" s="19"/>
+      <c r="S27" s="19"/>
     </row>
     <row r="28" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B28" t="s">
+        <v>37</v>
+      </c>
+      <c r="C28" t="s">
         <v>1</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" t="s">
         <v>2</v>
       </c>
-      <c r="D28" t="s">
-        <v>3</v>
-      </c>
-      <c r="E28" t="s">
-        <v>4</v>
-      </c>
       <c r="F28" t="s">
+        <v>6</v>
+      </c>
+      <c r="G28" t="s">
+        <v>7</v>
+      </c>
+      <c r="H28" t="s">
         <v>8</v>
       </c>
-      <c r="G28" t="s">
+      <c r="I28" t="s">
         <v>9</v>
       </c>
-      <c r="H28" t="s">
-        <v>10</v>
-      </c>
-      <c r="I28" t="s">
-        <v>11</v>
-      </c>
       <c r="K28" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L28" t="s">
+        <v>37</v>
+      </c>
+      <c r="M28" t="s">
         <v>1</v>
       </c>
-      <c r="M28" t="s">
+      <c r="N28" t="s">
+        <v>38</v>
+      </c>
+      <c r="O28" t="s">
         <v>2</v>
       </c>
-      <c r="N28" t="s">
-        <v>3</v>
-      </c>
-      <c r="O28" t="s">
-        <v>4</v>
-      </c>
       <c r="P28" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>7</v>
+      </c>
+      <c r="R28" t="s">
         <v>8</v>
       </c>
-      <c r="Q28" t="s">
+      <c r="S28" t="s">
         <v>9</v>
-      </c>
-      <c r="R28" t="s">
-        <v>10</v>
-      </c>
-      <c r="S28" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="B29">
-        <v>354</v>
+        <v>26</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
       </c>
       <c r="C29">
         <v>244</v>
       </c>
-      <c r="D29">
-        <v>253</v>
+      <c r="D29" t="s">
+        <v>44</v>
       </c>
       <c r="E29">
         <v>143</v>
@@ -2281,16 +2505,16 @@
         <v>0.60160000000000002</v>
       </c>
       <c r="K29" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="L29" s="7">
-        <v>226</v>
+        <v>26</v>
+      </c>
+      <c r="L29" s="7" t="s">
+        <v>70</v>
       </c>
       <c r="M29" s="7">
         <v>443</v>
       </c>
-      <c r="N29" s="7">
-        <v>54</v>
+      <c r="N29" s="7" t="s">
+        <v>71</v>
       </c>
       <c r="O29" s="7">
         <v>271</v>
@@ -2310,16 +2534,16 @@
     </row>
     <row r="30" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B30">
-        <v>536</v>
+        <v>27</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
       </c>
       <c r="C30">
         <v>483</v>
       </c>
-      <c r="D30">
-        <v>513</v>
+      <c r="D30" t="s">
+        <v>88</v>
       </c>
       <c r="E30">
         <v>460</v>
@@ -2337,16 +2561,16 @@
         <v>0.51149999999999995</v>
       </c>
       <c r="K30" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="L30">
-        <v>386</v>
+        <v>27</v>
+      </c>
+      <c r="L30" t="s">
+        <v>91</v>
       </c>
       <c r="M30">
         <v>891</v>
       </c>
-      <c r="N30">
-        <v>105</v>
+      <c r="N30" t="s">
+        <v>92</v>
       </c>
       <c r="O30">
         <v>610</v>
@@ -2366,16 +2590,16 @@
     </row>
     <row r="31" spans="1:19" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B31" s="10">
-        <v>85</v>
+        <v>28</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>89</v>
       </c>
       <c r="C31">
         <v>39</v>
       </c>
-      <c r="D31">
-        <v>66</v>
+      <c r="D31" t="s">
+        <v>90</v>
       </c>
       <c r="E31">
         <v>20</v>
@@ -2393,16 +2617,16 @@
         <v>0.59050000000000002</v>
       </c>
       <c r="K31" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="L31" s="10">
-        <v>42</v>
+        <v>28</v>
+      </c>
+      <c r="L31" s="10" t="s">
+        <v>93</v>
       </c>
       <c r="M31">
         <v>93</v>
       </c>
-      <c r="N31">
-        <v>12</v>
+      <c r="N31" t="s">
+        <v>94</v>
       </c>
       <c r="O31">
         <v>63</v>
